--- a/reports/devops-jobs-israel-2026-W35.xlsx
+++ b/reports/devops-jobs-israel-2026-W35.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-24T07:13:40</t>
+    <t xml:space="preserve">2026-08-25T07:01:20</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -390,205 +390,565 @@
     <t xml:space="preserve">2026-08-12</t>
   </si>
   <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4453871372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Python, Bash/Shell, Prometheus, Grafana, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5810373004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
+    <t xml:space="preserve">Appcharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earnix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eyesAtop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-zenity-4455197109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
   </si>
   <si>
     <t xml:space="preserve">Vetric</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vetric-4455613930</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
     <t xml:space="preserve">Connecteam</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Infra Engineer / DevOps Engineer</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-planck-4455682332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infra-engineer-devops-engineer-at-elbit-systems-israel-4442854342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-comblack-4458185867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer (37386)</t>
@@ -597,10 +957,7 @@
     <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456717268</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458217157</t>
   </si>
   <si>
     <t xml:space="preserve">Sr. Principal, DevOps</t>
@@ -618,595 +975,238 @@
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-blink-4442528208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4454269739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4454251693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4453871372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-compie-technologies-4455300779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4456464671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagry | Autonomous Driving</t>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-imagry-autonomous-driving-4452259211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devsecops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-dialog-4452580295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4443982712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-team-leader-at-radware-4442833696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-horizon-technologies-ltd-4455871682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization &amp; Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/virtualization-infrastructure-engineer-10296-at-bynet-data-communications-4455849080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Or HaNer, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4452238627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442909711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simplex 3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-simplex-3d-4452264625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Automation Engineer</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4453497245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterfall Security Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
     <t xml:space="preserve">Amazon Web Services (AWS)</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-automation-engineer-at-amazon-web-services-aws-4455938126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appcharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization &amp; Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/virtualization-infrastructure-engineer-10296-at-bynet-data-communications-4455849080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Lead Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-infrastructure-engineer-at-sela-4454743727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-infrastructure-engineer-at-shavit-software-4455295099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity &amp; Authentication Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/identity-authentication-infrastructure-engineer-at-logica-it-4452547813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
@@ -1245,6 +1245,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
   </si>
   <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -1296,43 +1305,19 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1350,16 +1335,13 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
     <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1527,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1535,7 +1517,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1071</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="10">
@@ -1607,7 +1589,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -1615,7 +1597,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1634,44 +1616,44 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>418</v>
+        <v>362</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1690,23 +1672,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B3" s="3">
         <v>23</v>
@@ -1717,12 +1699,12 @@
         <v>344</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>440</v>
+        <v>339</v>
       </c>
       <c r="B5" s="3">
         <v>20</v>
@@ -1730,63 +1712,63 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>339</v>
+        <v>438</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>443</v>
+        <v>336</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -1794,7 +1776,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3">
         <v>9</v>
@@ -1802,18 +1784,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>446</v>
+        <v>342</v>
       </c>
       <c r="B15" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>345</v>
+        <v>158</v>
       </c>
       <c r="B16" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1838,13 +1820,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2">
@@ -1852,13 +1834,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1867,79 +1849,79 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3">
-        <v>37.2</v>
+        <v>37.6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.2</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>33.6</v>
+        <v>42.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>18.2</v>
+        <v>17.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1948,7 +1930,7 @@
         <v>16.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2032,7 +2014,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2064,7 +2046,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2096,7 +2078,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -2128,7 +2110,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -2160,7 +2142,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -2192,7 +2174,7 @@
         <v>63</v>
       </c>
       <c r="J7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2224,7 +2206,7 @@
         <v>41</v>
       </c>
       <c r="J8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2256,7 +2238,7 @@
         <v>73</v>
       </c>
       <c r="J9" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -2288,7 +2270,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2320,7 +2302,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2352,7 +2334,7 @@
         <v>84</v>
       </c>
       <c r="J12" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -2384,7 +2366,7 @@
         <v>73</v>
       </c>
       <c r="J13" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -2416,7 +2398,7 @@
         <v>93</v>
       </c>
       <c r="J14" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -2448,7 +2430,7 @@
         <v>98</v>
       </c>
       <c r="J15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2480,7 +2462,7 @@
         <v>46</v>
       </c>
       <c r="J16" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -2512,7 +2494,7 @@
         <v>105</v>
       </c>
       <c r="J17" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -2544,7 +2526,7 @@
         <v>84</v>
       </c>
       <c r="J18" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2558,7 @@
         <v>112</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2608,7 +2590,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -2640,7 +2622,7 @@
         <v>122</v>
       </c>
       <c r="J21" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -2669,82 +2651,82 @@
         <v>126</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="J22" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="J23" s="3">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J24" s="3">
-        <v>73</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>90</v>
@@ -2768,7 +2750,7 @@
         <v>141</v>
       </c>
       <c r="J25" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -2776,10 +2758,10 @@
         <v>142</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2788,30 +2770,30 @@
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J26" s="3">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2829,42 +2811,42 @@
         <v>150</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="J27" s="3">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J28" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -2875,25 +2857,25 @@
         <v>156</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="J29" s="3">
         <v>5</v>
@@ -2901,103 +2883,103 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="J30" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>164</v>
       </c>
       <c r="J31" s="3">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J32" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -3010,24 +2992,24 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3040,57 +3022,57 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="J34" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J35" s="3">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>178</v>
+        <v>37</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3100,54 +3082,54 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="J36" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>141</v>
+        <v>186</v>
       </c>
       <c r="J37" s="3">
-        <v>25</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>123</v>
+        <v>187</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>49</v>
@@ -3160,57 +3142,57 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="J38" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J39" s="3">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>43</v>
@@ -3220,54 +3202,54 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="J40" s="3">
-        <v>3</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J41" s="3">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>49</v>
@@ -3280,54 +3262,56 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="J42" s="3">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="G43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>60</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>49</v>
@@ -3340,54 +3324,54 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J44" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="J45" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
@@ -3400,13 +3384,13 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -3414,10 +3398,10 @@
         <v>53</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -3430,54 +3414,54 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>49</v>
@@ -3485,20 +3469,18 @@
       <c r="E49" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="J49" s="3">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -3506,10 +3488,10 @@
         <v>53</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>49</v>
@@ -3522,13 +3504,13 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3536,13 +3518,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3552,24 +3534,24 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="C52" s="3" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
@@ -3582,117 +3564,117 @@
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="J54" s="3">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="J55" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3702,24 +3684,24 @@
         <v>23</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
       <c r="J56" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3732,13 +3714,13 @@
         <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58">
@@ -3749,284 +3731,280 @@
         <v>247</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>249</v>
+        <v>49</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>251</v>
+        <v>112</v>
       </c>
       <c r="J58" s="3">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>254</v>
-      </c>
+      <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J59" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>223</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>178</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>170</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="J63" s="3">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>266</v>
+        <v>170</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>269</v>
+        <v>63</v>
       </c>
       <c r="J64" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J65" s="3">
-        <v>27</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="J66" s="3">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>275</v>
+        <v>157</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>43</v>
@@ -4036,24 +4014,24 @@
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>277</v>
+        <v>56</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>180</v>
+        <v>269</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
@@ -4066,57 +4044,57 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>279</v>
+        <v>164</v>
       </c>
       <c r="J68" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="J69" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>56</v>
+        <v>274</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4126,13 +4104,13 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -4140,10 +4118,10 @@
         <v>53</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4156,10 +4134,10 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="J71" s="3">
         <v>0</v>
@@ -4167,16 +4145,16 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>38</v>
@@ -4186,54 +4164,54 @@
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="J72" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>213</v>
+        <v>63</v>
       </c>
       <c r="J73" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>293</v>
+        <v>170</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
@@ -4246,147 +4224,147 @@
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="J74" s="3">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>160</v>
+        <v>292</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>298</v>
+        <v>63</v>
       </c>
       <c r="J75" s="3">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>123</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>123</v>
+        <v>297</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>168</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>302</v>
+        <v>162</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="J77" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>178</v>
+        <v>49</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>123</v>
+        <v>302</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>160</v>
+        <v>304</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
@@ -4396,57 +4374,57 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
@@ -4456,40 +4434,40 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>80</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="J82" s="3">
         <v>0</v>
@@ -4497,46 +4475,46 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="J83" s="3">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>167</v>
+        <v>319</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>49</v>
+        <v>184</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4546,100 +4524,100 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>324</v>
+        <v>212</v>
       </c>
       <c r="J84" s="3">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="J87" s="3">
         <v>6</v>
@@ -4647,16 +4625,16 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4666,13 +4644,13 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4772,7 +4750,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -4806,13 +4784,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4820,18 +4798,18 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>203</v>
+        <v>252</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4839,18 +4817,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>123</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4858,18 +4836,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4877,18 +4855,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>191</v>
+        <v>279</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4896,18 +4874,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4915,18 +4893,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>297</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>283</v>
+        <v>168</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4934,18 +4912,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>306</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4953,18 +4931,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4972,18 +4950,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>192</v>
+        <v>320</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4991,7 +4969,7 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5020,63 +4998,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>158</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5084,47 +5062,47 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5132,7 +5110,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5140,7 +5118,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5153,7 +5131,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5162,7 +5140,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
@@ -5183,15 +5161,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5199,15 +5177,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5215,7 +5193,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5223,7 +5201,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5231,7 +5209,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5239,7 +5217,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5247,7 +5225,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5255,7 +5233,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5263,7 +5241,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>191</v>
+        <v>235</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5271,7 +5249,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5279,7 +5257,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5293,23 +5271,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
@@ -5373,7 +5351,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C6" s="3">
         <v>6.0</v>
@@ -5401,13 +5379,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="C8" s="3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -5415,10 +5393,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="C9" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -5429,13 +5407,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5443,13 +5421,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5457,7 +5435,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C12" s="3">
         <v>2.8</v>
@@ -5471,7 +5449,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>282</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5485,13 +5463,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5499,10 +5477,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5513,10 +5491,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="C16" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -5539,10 +5517,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
@@ -5561,10 +5539,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4">
@@ -5572,10 +5550,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -5594,7 +5572,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
@@ -5602,15 +5580,15 @@
         <v>49</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -5618,15 +5596,15 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5639,18 +5617,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5674,10 +5644,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5689,10 +5659,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5709,31 +5679,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>90</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
@@ -5741,31 +5711,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4">
@@ -5773,28 +5743,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>80</v>
@@ -5805,31 +5775,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>376</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
@@ -5837,31 +5807,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7">
@@ -5869,31 +5839,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>167</v>
+        <v>250</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>323</v>
+        <v>378</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8">
@@ -5910,13 +5880,13 @@
         <v>90</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F8" s="3">
         <v>92</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>24</v>
@@ -5933,31 +5903,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F9" s="3">
         <v>92</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -5974,13 +5944,13 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F10" s="3">
         <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
@@ -5997,31 +5967,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>392</v>
+        <v>329</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F11" s="3">
         <v>81</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
@@ -6029,31 +5999,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
+        <v>320</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>279</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -6061,31 +6031,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>403</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14">
@@ -6093,31 +6063,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>122</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15">
@@ -6125,31 +6095,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>225</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -6157,31 +6127,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>294</v>
+        <v>408</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>415</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17">
@@ -6189,31 +6159,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="F17" s="3">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18">
@@ -6221,31 +6191,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>422</v>
+        <v>188</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>314</v>
+        <v>162</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F18" s="3">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>80</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19">
@@ -6253,31 +6223,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>427</v>
+        <v>183</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20">
@@ -6285,31 +6255,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>434</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -6317,31 +6287,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>158</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W35.xlsx
+++ b/reports/devops-jobs-israel-2026-W35.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-25T07:01:20</t>
+    <t xml:space="preserve">2026-08-26T07:01:53</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -195,15 +195,24 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
   </si>
   <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Full Stack Developer – Core Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Postgres, MySQL, Kafka, RabbitMQ, Crossplane</t>
   </si>
   <si>
@@ -486,838 +495,868 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer – Kubernetes &amp; AI - 4664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Software Systems Ltd.</t>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vetric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vetric-4455613930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37386)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458217157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4453871372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458219168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. SRE AI Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-comblack-4458185867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4456917658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization &amp; Infrastructure Engineer (10296)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bynet Data Communications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/virtualization-infrastructure-engineer-10296-at-bynet-data-communications-4455849080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4453497245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%E2%80%93-kubernetes-ai-4664-at-bynet-software-systems-ltd-4454492747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4453871372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appcharge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-appcharge-4454760249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-akamai-technologies-4458268923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
   </si>
   <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4455709981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-claroty-4452584141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earnix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-earnix-4437761619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eyesAtop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-eyesatop-4454764581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-zenity-4455197109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vetric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vetric-4455613930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-planck-4455682332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-comblack-4458185867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-jobgether-4454997118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37386)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458217157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4437772282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizon Technologies LTD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-horizon-technologies-ltd-4455871682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization &amp; Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/virtualization-infrastructure-engineer-10296-at-bynet-data-communications-4455849080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-administrator-at-abra-4454749355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4453497245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4455765409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterfall Security Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-position-at-waterfall-security-solutions-4444878648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4451682760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist – MENTEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-%E2%80%93-mentee-at-mobileye-4445729205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1326,22 +1365,22 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1493,7 +1532,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1501,7 +1540,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1509,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1556,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1060</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="10">
@@ -1589,7 +1628,7 @@
         <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1597,7 +1636,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1646,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1616,31 +1655,31 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1649,14 +1688,6 @@
       </c>
       <c r="B5" s="3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1672,130 +1703,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>448</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>435</v>
+        <v>362</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>439</v>
+        <v>358</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>337</v>
+        <v>452</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>158</v>
+        <v>364</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1820,13 +1851,13 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2">
@@ -1834,13 +1865,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>15.2</v>
+        <v>11.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1849,88 +1880,88 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
-        <v>37.6</v>
+        <v>35.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.0</v>
+        <v>8.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.0</v>
+        <v>1.8</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>42.5</v>
+        <v>39.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.0</v>
+        <v>21.3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.1</v>
+        <v>17.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1943,7 +1974,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2014,7 +2045,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2046,7 +2077,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2078,7 +2109,7 @@
         <v>52</v>
       </c>
       <c r="J4" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -2110,7 +2141,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2142,18 +2173,18 @@
         <v>41</v>
       </c>
       <c r="J6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>49</v>
@@ -2162,91 +2193,91 @@
         <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="J7" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J9" s="3">
-        <v>72</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>49</v>
@@ -2270,15 +2301,15 @@
         <v>76</v>
       </c>
       <c r="J10" s="3">
-        <v>2</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>49</v>
@@ -2290,27 +2321,27 @@
         <v>38</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="J11" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>49</v>
@@ -2322,27 +2353,27 @@
         <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J12" s="3">
-        <v>89</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>49</v>
@@ -2354,19 +2385,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="J13" s="3">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -2374,10 +2405,10 @@
         <v>88</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>49</v>
@@ -2386,80 +2417,80 @@
         <v>38</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J14" s="3">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J15" s="3">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="J16" s="3">
         <v>29</v>
@@ -2470,10 +2501,10 @@
         <v>102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>49</v>
@@ -2491,21 +2522,21 @@
         <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="J17" s="3">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>49</v>
@@ -2514,16 +2545,16 @@
         <v>38</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="J18" s="3">
         <v>89</v>
@@ -2531,13 +2562,13 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>49</v>
@@ -2546,190 +2577,190 @@
         <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J20" s="3">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J21" s="3">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="J22" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="J23" s="3">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J24" s="3">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>49</v>
@@ -2738,30 +2769,30 @@
         <v>38</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="J25" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>49</v>
@@ -2770,30 +2801,30 @@
         <v>38</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J26" s="3">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>49</v>
@@ -2802,19 +2833,19 @@
         <v>38</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J27" s="3">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
@@ -2822,19 +2853,19 @@
         <v>151</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>125</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>24</v>
@@ -2843,143 +2874,143 @@
         <v>153</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="J28" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="J29" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="D30" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="J30" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>164</v>
       </c>
       <c r="J31" s="3">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J32" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>49</v>
@@ -2992,24 +3023,24 @@
         <v>23</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>49</v>
@@ -3022,30 +3053,30 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3055,24 +3086,24 @@
         <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>62</v>
       </c>
       <c r="J35" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>43</v>
@@ -3082,10 +3113,10 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="J36" s="3">
         <v>26</v>
@@ -3093,76 +3124,76 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="J37" s="3">
-        <v>90</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>186</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="J38" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>43</v>
@@ -3172,54 +3203,54 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J39" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J40" s="3">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>49</v>
@@ -3232,116 +3263,114 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J41" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>206</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="J43" s="3">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>49</v>
@@ -3357,27 +3386,27 @@
         <v>214</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="J45" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>215</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3387,10 +3416,10 @@
         <v>216</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -3401,7 +3430,7 @@
         <v>217</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>49</v>
@@ -3417,84 +3446,84 @@
         <v>218</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>221</v>
+        <v>62</v>
       </c>
       <c r="J48" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>224</v>
+        <v>66</v>
       </c>
       <c r="J49" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>38</v>
@@ -3504,13 +3533,13 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3518,13 +3547,13 @@
         <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>38</v>
@@ -3534,147 +3563,147 @@
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="J51" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J52" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="J53" s="3">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="J54" s="3">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>238</v>
+        <v>177</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="J55" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>240</v>
+        <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>38</v>
@@ -3687,10 +3716,10 @@
         <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="J56" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3698,10 +3727,10 @@
         <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>49</v>
@@ -3728,16 +3757,16 @@
         <v>246</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3747,10 +3776,10 @@
         <v>248</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>112</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59">
@@ -3761,7 +3790,7 @@
         <v>250</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>49</v>
@@ -3777,24 +3806,24 @@
         <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>38</v>
@@ -3804,57 +3833,57 @@
         <v>23</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>170</v>
+        <v>257</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="J61" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>178</v>
+        <v>262</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>38</v>
@@ -3864,27 +3893,27 @@
         <v>23</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>38</v>
@@ -3894,57 +3923,57 @@
         <v>23</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J63" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>170</v>
+        <v>264</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>168</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>38</v>
@@ -3954,84 +3983,86 @@
         <v>23</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="J65" s="3">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>170</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>264</v>
+        <v>180</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="J66" s="3">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>129</v>
+        <v>275</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>38</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="G67" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>212</v>
+        <v>278</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>269</v>
+        <v>194</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>49</v>
@@ -4044,57 +4075,57 @@
         <v>23</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>164</v>
+        <v>87</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="J69" s="3">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>274</v>
+        <v>53</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>276</v>
+        <v>202</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>38</v>
@@ -4104,13 +4135,13 @@
         <v>23</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>195</v>
+        <v>62</v>
       </c>
       <c r="J70" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4118,10 +4149,10 @@
         <v>53</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>49</v>
@@ -4134,54 +4165,54 @@
         <v>23</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="J71" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>283</v>
+        <v>168</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>229</v>
+        <v>56</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>49</v>
@@ -4194,57 +4225,57 @@
         <v>23</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>63</v>
+        <v>293</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>289</v>
+        <v>205</v>
       </c>
       <c r="J74" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>292</v>
+        <v>168</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>43</v>
@@ -4254,27 +4285,27 @@
         <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>63</v>
+        <v>299</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>295</v>
+        <v>194</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>277</v>
+        <v>49</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>38</v>
@@ -4284,54 +4315,54 @@
         <v>23</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>297</v>
+        <v>158</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>168</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>49</v>
@@ -4344,27 +4375,27 @@
         <v>23</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>43</v>
@@ -4374,27 +4405,27 @@
         <v>23</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>43</v>
@@ -4404,27 +4435,27 @@
         <v>23</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="J80" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>283</v>
+        <v>190</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>43</v>
@@ -4434,27 +4465,27 @@
         <v>23</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>310</v>
+        <v>158</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>157</v>
+        <v>317</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>43</v>
@@ -4464,27 +4495,27 @@
         <v>23</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>212</v>
+        <v>164</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>38</v>
@@ -4494,27 +4525,27 @@
         <v>23</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="J83" s="3">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>318</v>
+        <v>158</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>320</v>
+        <v>197</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>43</v>
@@ -4524,57 +4555,59 @@
         <v>23</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>47</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>112</v>
+        <v>329</v>
       </c>
       <c r="J85" s="3">
-        <v>8</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>43</v>
@@ -4584,27 +4617,27 @@
         <v>23</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>38</v>
@@ -4614,27 +4647,27 @@
         <v>23</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>303</v>
+        <v>337</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>332</v>
+        <v>59</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>43</v>
@@ -4644,17 +4677,197 @@
         <v>23</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J89" s="3">
         <v>2</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="J90" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J91" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J92" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J93" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J94" s="3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J88"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4743,6 +4956,12 @@
     <hyperlink ref="H86" r:id="rId85"/>
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4750,7 +4969,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
@@ -4784,32 +5003,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -4817,18 +5036,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -4836,18 +5055,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -4855,18 +5074,18 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4874,18 +5093,18 @@
         <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>189</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>283</v>
+        <v>190</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4893,18 +5112,18 @@
         <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>168</v>
+        <v>266</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -4912,18 +5131,18 @@
         <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -4931,18 +5150,18 @@
         <v>23</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>310</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -4950,18 +5169,18 @@
         <v>23</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>320</v>
+        <v>202</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -4969,11 +5188,30 @@
         <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -4985,6 +5223,7 @@
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4998,31 +5237,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>158</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -5030,15 +5269,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>327</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5046,79 +5285,79 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>340</v>
+        <v>276</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5131,7 +5370,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5140,12 +5379,12 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5153,7 +5392,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5161,7 +5400,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5177,7 +5416,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5193,7 +5432,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5201,7 +5440,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5209,7 +5448,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5217,7 +5456,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5225,7 +5464,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5233,7 +5472,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5241,7 +5480,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5249,7 +5488,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5257,7 +5496,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5271,23 +5510,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
@@ -5295,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3">
         <v>18.6</v>
@@ -5309,7 +5548,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3">
         <v>16.8</v>
@@ -5337,10 +5576,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C5" s="3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -5351,10 +5590,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5365,10 +5604,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C7" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5379,13 +5618,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="C8" s="3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -5393,13 +5632,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="C9" s="3">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5407,10 +5646,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5421,13 +5660,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>5.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5435,13 +5674,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="C12" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5449,10 +5688,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5463,13 +5702,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5477,10 +5716,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5491,7 +5730,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5517,15 +5756,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -5539,10 +5778,10 @@
         <v>43</v>
       </c>
       <c r="B3" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4">
@@ -5550,10 +5789,10 @@
         <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5572,7 +5811,7 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -5585,10 +5824,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -5596,20 +5835,20 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5617,10 +5856,26 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5632,9 +5887,9 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -5644,10 +5899,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -5659,10 +5914,10 @@
         <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>21</v>
@@ -5679,31 +5934,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">
@@ -5711,31 +5966,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>365</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -5743,31 +5998,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>300</v>
+        <v>386</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>80</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -5775,31 +6030,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>369</v>
+        <v>314</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>370</v>
+        <v>231</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -5807,31 +6062,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>373</v>
+        <v>97</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>374</v>
+        <v>92</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="F6" s="3">
+        <v>92</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -5839,31 +6094,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F7" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>378</v>
+        <v>315</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -5871,31 +6126,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F8" s="3">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -5903,31 +6158,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>383</v>
+        <v>190</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="F9" s="3">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>386</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -5935,7 +6190,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>399</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
@@ -5944,22 +6199,22 @@
         <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F10" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>45</v>
+        <v>401</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -5967,31 +6222,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>329</v>
+        <v>403</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F11" s="3">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>245</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
@@ -5999,31 +6254,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F12" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13">
@@ -6031,31 +6286,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>412</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F13" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>245</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
@@ -6063,31 +6318,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>403</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15">
@@ -6095,31 +6350,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>315</v>
+        <v>185</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
@@ -6127,31 +6382,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="F16" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>224</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17">
@@ -6159,31 +6414,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>209</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
@@ -6191,31 +6446,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>188</v>
+        <v>432</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>162</v>
+        <v>433</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>418</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -6223,31 +6478,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="F19" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20">
@@ -6255,31 +6510,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="F20" s="3">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>80</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21">
@@ -6287,31 +6542,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W35.xlsx
+++ b/reports/devops-jobs-israel-2026-W35.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-26T07:01:53</t>
+    <t xml:space="preserve">2026-08-27T17:34:35</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,15 +57,12 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1%</t>
+    <t xml:space="preserve">0.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Salary disclosure rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -282,7 +279,7 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28</t>
+    <t xml:space="preserve">2026-08-27</t>
   </si>
   <si>
     <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
@@ -312,978 +309,1020 @@
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Engineer - Billing Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537525003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4457221102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ControlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4459877158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4459308737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4459018156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moon Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yad2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scytale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4459803825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4456815057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
     <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, CI/CD, Linux, Python, Helm</t>
+    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineer - Billing Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Python, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8620283002?gh_jid=8620283002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, CI/CD, Linux, Python, Bash/Shell, Networking, Security, Argo CD, Observability, Tracing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8695882002?gh_jid=8695882002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vetric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vetric-4455613930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4428832411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4456470553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4446898048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-akamai-technologies-4458268923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
   </si>
   <si>
     <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-harmonic-4360460066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37386)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37386-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458217157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-descope-4431665949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior\Lead DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-lead-devops-engineer-at-elbit-systems-israel-4375574113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4453871372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4455619482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4458219168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer, AI Agent Platforms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-agent-platforms-at-nvidia-4442919276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. SRE AI Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-sre-ai-engineer-at-navan-4437742346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4457410161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-mobileye-4436210389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Principal DevOps Engineer (Cortex Cloud)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-devops-engineer-cortex-cloud-at-palo-alto-networks-4443693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Cloud Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-engineer-at-comblack-4458185867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-personetics-4428829912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4456917658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization &amp; Infrastructure Engineer (10296)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/virtualization-infrastructure-engineer-10296-at-bynet-data-communications-4455849080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps / Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-tairc-4453497245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-akamai-technologies-4458268923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1293,6 +1332,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -1312,51 +1363,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1532,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -1540,7 +1546,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -1548,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1556,7 +1562,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1047</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10">
@@ -1564,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1580,7 +1586,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1589,26 +1595,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1617,26 +1623,26 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1646,48 +1652,56 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1703,63 +1717,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>276</v>
+        <v>451</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>449</v>
+        <v>284</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -1767,66 +1781,66 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>453</v>
+        <v>352</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1845,123 +1859,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>11.1</v>
+        <v>20.1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>35.2</v>
+        <v>38.2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>39.1</v>
+        <v>30.6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>21.3</v>
+        <v>16.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>17.9</v>
+        <v>15.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -1986,633 +2000,633 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="J2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J3" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="C4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J4" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="I6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="J7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J8" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J10" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J13" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="I14" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J14" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>96</v>
-      </c>
       <c r="J15" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="J17" s="3">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="J18" s="3">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J19" s="3">
-        <v>90</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>114</v>
@@ -2621,7 +2635,7 @@
         <v>115</v>
       </c>
       <c r="J20" s="3">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -2629,527 +2643,531 @@
         <v>116</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="J21" s="3">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="J22" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J23" s="3">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="J24" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J25" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="J26" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>80</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="J28" s="3">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="J31" s="3">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J33" s="3">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="J34" s="3">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="J36" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J37" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -3160,691 +3178,693 @@
         <v>184</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>186</v>
+        <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="J41" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="G42" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="J44" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>53</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="J46" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="J47" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>226</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>62</v>
+        <v>164</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>230</v>
+        <v>168</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="J52" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>222</v>
+        <v>126</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J53" s="3">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="C54" s="3" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="J54" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="J55" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>245</v>
+        <v>86</v>
       </c>
       <c r="J57" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>246</v>
+        <v>168</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>247</v>
+        <v>170</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>245</v>
+        <v>167</v>
       </c>
       <c r="J58" s="3">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>252</v>
+        <v>86</v>
       </c>
       <c r="J59" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>86</v>
       </c>
       <c r="J60" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>257</v>
+        <v>168</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>258</v>
@@ -3853,170 +3873,170 @@
         <v>259</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="J62" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="D65" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J65" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>180</v>
+        <v>274</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="J66" s="3">
         <v>1</v>
@@ -4024,331 +4044,331 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="D67" s="3" t="s">
-        <v>275</v>
+        <v>126</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>276</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>278</v>
+        <v>86</v>
       </c>
       <c r="J67" s="3">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>194</v>
+        <v>282</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>160</v>
+        <v>283</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>253</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F68" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="G68" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>87</v>
+        <v>286</v>
       </c>
       <c r="J68" s="3">
-        <v>90</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>282</v>
+        <v>173</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="J69" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>53</v>
+        <v>289</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>284</v>
+        <v>162</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>62</v>
+        <v>291</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>288</v>
+        <v>164</v>
       </c>
       <c r="J71" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>289</v>
+        <v>52</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="J72" s="3">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="J73" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="J74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>299</v>
+        <v>86</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="J76" s="3">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>158</v>
+        <v>52</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="J77" s="3">
         <v>2</v>
@@ -4356,271 +4376,271 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>188</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>309</v>
+        <v>189</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J79" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>192</v>
+        <v>78</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>314</v>
+        <v>52</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>316</v>
+        <v>169</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>317</v>
+        <v>189</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="J82" s="3">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>320</v>
+        <v>217</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>323</v>
+        <v>219</v>
       </c>
       <c r="J83" s="3">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>47</v>
+        <v>326</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="I85" s="3" t="s">
-        <v>329</v>
+        <v>86</v>
       </c>
       <c r="J85" s="3">
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>52</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="J86" s="3">
         <v>0</v>
@@ -4628,59 +4648,61 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="J87" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F88" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="G88" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4688,186 +4710,126 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="J89" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>314</v>
+        <v>201</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>231</v>
+        <v>338</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J90" s="3">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>348</v>
+        <v>58</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J93" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="J94" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J92"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4960,8 +4922,6 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4969,9 +4929,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4980,55 +4940,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5036,18 +4996,18 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>185</v>
+        <v>92</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5055,18 +5015,18 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>213</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5074,144 +5034,448 @@
         <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>266</v>
+        <v>188</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>268</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>168</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>266</v>
+        <v>191</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>270</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>209</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>285</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>330</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>331</v>
+        <v>212</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>332</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>338</v>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G28"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5224,6 +5488,22 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
+    <hyperlink ref="G27" r:id="rId26"/>
+    <hyperlink ref="G28" r:id="rId27"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5237,71 +5517,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>360</v>
+        <v>177</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>363</v>
+        <v>284</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5309,7 +5589,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>128</v>
+        <v>354</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5317,15 +5597,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5333,7 +5613,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5341,7 +5621,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5349,15 +5629,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5370,21 +5650,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5392,7 +5672,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5400,15 +5680,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5416,7 +5696,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5424,7 +5704,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5432,7 +5712,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5440,7 +5720,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5448,7 +5728,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5456,7 +5736,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5464,7 +5744,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5472,7 +5752,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5480,7 +5760,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5488,7 +5768,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5496,7 +5776,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5510,23 +5790,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2">
@@ -5534,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3">
         <v>18.6</v>
@@ -5548,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3">
         <v>16.8</v>
@@ -5562,7 +5842,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="3">
         <v>10.9</v>
@@ -5576,13 +5856,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C5" s="3">
-        <v>7.4</v>
+        <v>10.4</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5590,10 +5870,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5604,10 +5884,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -5618,7 +5898,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C8" s="3">
         <v>5.8</v>
@@ -5632,13 +5912,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="C9" s="3">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5646,10 +5926,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3">
-        <v>5.3</v>
+        <v>5.0</v>
       </c>
       <c r="D10" s="3">
         <v>2</v>
@@ -5660,13 +5940,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C11" s="3">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5674,13 +5954,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5688,10 +5968,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>273</v>
+        <v>162</v>
       </c>
       <c r="C13" s="3">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5702,7 +5982,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>189</v>
+        <v>267</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5716,10 +5996,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -5730,7 +6010,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5753,46 +6033,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="B2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -5808,15 +6088,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
         <v>61</v>
@@ -5824,7 +6104,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3">
         <v>17</v>
@@ -5832,7 +6112,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5840,15 +6120,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -5856,7 +6136,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -5864,15 +6144,15 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5889,7 +6169,7 @@
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -5899,34 +6179,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -5934,31 +6214,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
@@ -5966,31 +6246,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>305</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>278</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -5998,31 +6278,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -6030,31 +6310,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
@@ -6062,31 +6342,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>386</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>92</v>
+        <v>387</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>100</v>
+        <v>389</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
@@ -6094,31 +6374,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>314</v>
+        <v>390</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>312</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>190</v>
+        <v>92</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
@@ -6126,31 +6406,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>386</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>191</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>393</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>45</v>
+        <v>394</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
@@ -6158,31 +6438,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>394</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F9" s="3">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="F9" s="3">
-        <v>81</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>398</v>
+        <v>44</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>252</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -6190,31 +6470,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F10" s="3">
+        <v>81</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F10" s="3">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>252</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11">
@@ -6222,31 +6502,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="F11" s="3">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>404</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>405</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -6257,28 +6537,28 @@
         <v>406</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F12" s="3">
+        <v>60</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F12" s="3">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>410</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13">
@@ -6286,31 +6566,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F13" s="3">
+        <v>54</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F13" s="3">
-        <v>48</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -6318,31 +6598,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F14" s="3">
+        <v>52</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F14" s="3">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="15">
@@ -6350,31 +6630,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F15" s="3">
+        <v>48</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F15" s="3">
-        <v>41</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16">
@@ -6382,31 +6662,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F16" s="3">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>427</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17">
@@ -6414,31 +6694,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>429</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>430</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -6455,22 +6735,22 @@
         <v>433</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19">
@@ -6478,31 +6758,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>190</v>
+        <v>268</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
@@ -6510,31 +6790,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>259</v>
+        <v>158</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>442</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21">
@@ -6542,31 +6822,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>259</v>
+        <v>158</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>445</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W35.xlsx
+++ b/reports/devops-jobs-israel-2026-W35.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="473">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-27T17:34:35</t>
+    <t xml:space="preserve">2026-08-28T18:33:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -327,7 +327,7 @@
     <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-29</t>
+    <t xml:space="preserve">2026-08-28</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
@@ -516,6 +516,24 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matia</t>
   </si>
   <si>
@@ -525,9 +543,6 @@
     <t xml:space="preserve">2026-08-06</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log-On Software</t>
   </si>
   <si>
@@ -558,211 +573,415 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ControlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4459877158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead (37248)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4459803825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zadara-4448858731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-zenity-4455197109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4459018156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4459308737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KMS Lighthouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4456815057</t>
+  </si>
+  <si>
     <t xml:space="preserve">Checkmarx</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - KubeOps Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-kubeops-team-at-wix-4453083488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ControlUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4459877158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4459308737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4459018156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moon-active-4447023421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yad2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-yad2-4439486812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
   </si>
   <si>
     <t xml:space="preserve">Scytale</t>
@@ -771,598 +990,400 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
   </si>
   <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZOLL Medical Corporation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zoll-medical-corporation-4399156755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4459803825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4442990421</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4456917658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, GCP, Cloud (any), Networking, Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-viz-ai-4437383686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4456815057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4428485007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-cloud-engineer-at-moon-active-4447031167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Facing System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4457742934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-akamai-technologies-4458268923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1380,13 +1401,16 @@
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
     <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1538,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1546,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1554,7 +1578,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1562,7 +1586,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1056</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="10">
@@ -1634,7 +1658,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1661,36 +1685,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1698,7 +1722,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1717,130 +1741,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>461</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>454</v>
+        <v>353</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>350</v>
+        <v>463</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1865,13 +1889,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2">
@@ -1882,10 +1906,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>20.1</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1894,88 +1918,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>9.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.6</v>
+        <v>43.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.2</v>
+        <v>19.2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2059,7 +2083,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2091,7 +2115,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2123,7 +2147,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -2155,7 +2179,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -2187,7 +2211,7 @@
         <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2219,7 +2243,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2251,7 +2275,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2283,7 +2307,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2315,7 +2339,7 @@
         <v>75</v>
       </c>
       <c r="J10" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -2347,7 +2371,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2379,7 +2403,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2411,7 +2435,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2443,7 +2467,7 @@
         <v>75</v>
       </c>
       <c r="J14" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -2475,7 +2499,7 @@
         <v>95</v>
       </c>
       <c r="J15" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -2507,7 +2531,7 @@
         <v>45</v>
       </c>
       <c r="J16" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -2539,7 +2563,7 @@
         <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2571,7 +2595,7 @@
         <v>86</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2603,7 +2627,7 @@
         <v>109</v>
       </c>
       <c r="J19" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -2635,7 +2659,7 @@
         <v>115</v>
       </c>
       <c r="J20" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -2667,7 +2691,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -2699,7 +2723,7 @@
         <v>65</v>
       </c>
       <c r="J22" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2731,7 +2755,7 @@
         <v>129</v>
       </c>
       <c r="J23" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
@@ -2763,7 +2787,7 @@
         <v>86</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2795,7 +2819,7 @@
         <v>137</v>
       </c>
       <c r="J25" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -2827,7 +2851,7 @@
         <v>86</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2859,7 +2883,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2891,7 +2915,7 @@
         <v>149</v>
       </c>
       <c r="J28" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
@@ -2923,7 +2947,7 @@
         <v>40</v>
       </c>
       <c r="J29" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -2955,7 +2979,7 @@
         <v>156</v>
       </c>
       <c r="J30" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2985,7 +3009,7 @@
         <v>160</v>
       </c>
       <c r="J31" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -3015,7 +3039,7 @@
         <v>164</v>
       </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -3056,10 +3080,10 @@
         <v>169</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>42</v>
@@ -3069,10 +3093,10 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -3080,10 +3104,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>52</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>158</v>
@@ -3099,83 +3123,81 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J37" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>158</v>
@@ -3184,64 +3206,66 @@
         <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="J38" s="3">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="J39" s="3">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>42</v>
@@ -3251,27 +3275,27 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>42</v>
@@ -3281,45 +3305,43 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="J41" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>198</v>
+        <v>86</v>
       </c>
       <c r="J42" s="3">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -3330,7 +3352,7 @@
         <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
@@ -3343,60 +3365,60 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J44" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3406,18 +3428,18 @@
         <v>208</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>158</v>
@@ -3433,54 +3455,56 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>86</v>
+        <v>215</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>214</v>
+        <v>52</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
@@ -3493,27 +3517,27 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="J48" s="3">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>42</v>
@@ -3523,117 +3547,117 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>219</v>
+        <v>61</v>
       </c>
       <c r="J49" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>164</v>
+        <v>229</v>
       </c>
       <c r="J50" s="3">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="J51" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="J52" s="3">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3643,60 +3667,60 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="J53" s="3">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>232</v>
+        <v>52</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>236</v>
+        <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>239</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
@@ -3706,7 +3730,7 @@
         <v>240</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="J55" s="3">
         <v>1</v>
@@ -3714,16 +3738,16 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C56" s="3" t="s">
-        <v>238</v>
+        <v>158</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>239</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3733,60 +3757,60 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="J56" s="3">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>247</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
@@ -3796,51 +3820,51 @@
         <v>249</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="J58" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>252</v>
+        <v>158</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>253</v>
+        <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -3853,57 +3877,57 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>262</v>
+        <v>61</v>
       </c>
       <c r="J61" s="3">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>263</v>
+        <v>52</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
@@ -3913,27 +3937,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>266</v>
+        <v>52</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
@@ -3943,24 +3967,24 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>126</v>
@@ -3973,27 +3997,27 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
@@ -4003,27 +4027,27 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>61</v>
+        <v>267</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4033,24 +4057,24 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>126</v>
@@ -4063,59 +4087,57 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>253</v>
+        <v>36</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>284</v>
-      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="J68" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>158</v>
+        <v>270</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
@@ -4125,51 +4147,53 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>158</v>
+        <v>281</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>282</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="J70" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>55</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>158</v>
@@ -4185,21 +4209,21 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>52</v>
+        <v>288</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>158</v>
@@ -4208,58 +4232,58 @@
         <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>296</v>
+        <v>86</v>
       </c>
       <c r="J72" s="3">
-        <v>62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>55</v>
+        <v>168</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>297</v>
+        <v>244</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="J73" s="3">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>158</v>
@@ -4275,27 +4299,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>164</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>42</v>
@@ -4305,24 +4329,24 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J75" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>255</v>
+        <v>168</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>224</v>
+        <v>299</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>48</v>
@@ -4335,54 +4359,54 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>306</v>
+        <v>102</v>
       </c>
       <c r="J76" s="3">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>52</v>
+        <v>252</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>168</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
@@ -4395,27 +4419,27 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>160</v>
+        <v>267</v>
       </c>
       <c r="J78" s="3">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>188</v>
+        <v>306</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>42</v>
@@ -4425,21 +4449,21 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>162</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>158</v>
@@ -4448,34 +4472,34 @@
         <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>78</v>
+        <v>310</v>
       </c>
       <c r="J80" s="3">
-        <v>4</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>311</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>317</v>
+        <v>178</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>37</v>
@@ -4485,10 +4509,10 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J81" s="3">
         <v>0</v>
@@ -4496,13 +4520,13 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>206</v>
+        <v>313</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>126</v>
@@ -4515,27 +4539,27 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>320</v>
+        <v>168</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>42</v>
@@ -4545,56 +4569,54 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="J83" s="3">
-        <v>27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>189</v>
+        <v>319</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>324</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>268</v>
+        <v>175</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>126</v>
@@ -4607,81 +4629,83 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="J85" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>52</v>
+        <v>210</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>328</v>
+        <v>174</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>168</v>
+        <v>324</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J87" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>158</v>
@@ -4692,17 +4716,15 @@
       <c r="E88" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>177</v>
-      </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J88" s="3">
         <v>0</v>
@@ -4710,16 +4732,16 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>336</v>
+        <v>261</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>239</v>
+        <v>126</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>42</v>
@@ -4729,21 +4751,21 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>158</v>
@@ -4752,34 +4774,36 @@
         <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>340</v>
+        <v>86</v>
       </c>
       <c r="J90" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>42</v>
@@ -4789,24 +4813,24 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
@@ -4819,17 +4843,107 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J92" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J93" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="B94" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="I95" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J92" s="3">
-        <v>1</v>
+      <c r="J95" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J95"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -4922,6 +5036,9 @@
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
     <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4929,9 +5046,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -4963,13 +5080,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -4977,75 +5094,75 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>131</v>
+        <v>299</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>92</v>
+        <v>158</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>311</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>139</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>328</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>169</v>
+        <v>329</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5053,457 +5170,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>342</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G28"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
-    <hyperlink ref="G26" r:id="rId25"/>
-    <hyperlink ref="G27" r:id="rId26"/>
-    <hyperlink ref="G28" r:id="rId27"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5517,15 +5194,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
@@ -5533,7 +5210,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5541,7 +5218,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5549,7 +5226,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -5557,7 +5234,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5565,7 +5242,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5573,7 +5250,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B8" s="3">
         <v>14</v>
@@ -5581,7 +5258,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5589,7 +5266,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5605,7 +5282,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5613,7 +5290,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5621,7 +5298,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5629,7 +5306,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -5637,7 +5314,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5650,7 +5327,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5659,7 +5336,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -5680,15 +5357,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>178</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5696,7 +5373,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5752,7 +5429,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5760,7 +5437,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5768,7 +5445,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5776,7 +5453,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5797,16 +5474,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2">
@@ -5926,13 +5603,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3">
-        <v>5.0</v>
+        <v>5.3</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -5940,13 +5617,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C11" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5954,7 +5631,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C12" s="3">
         <v>2.9</v>
@@ -5982,7 +5659,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C14" s="3">
         <v>2.8</v>
@@ -5996,7 +5673,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6010,7 +5687,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6036,21 +5713,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -6058,10 +5735,10 @@
         <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
@@ -6069,10 +5746,10 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -6091,7 +5768,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -6099,7 +5776,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -6112,7 +5789,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6120,39 +5797,39 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>222</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="B8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -6179,10 +5856,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6194,10 +5871,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6223,13 +5900,13 @@
         <v>92</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
@@ -6246,28 +5923,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>82</v>
@@ -6278,31 +5955,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>384</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -6310,31 +5987,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
@@ -6342,31 +6019,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>386</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>389</v>
+        <v>44</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -6374,31 +6051,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>91</v>
+        <v>393</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>92</v>
+        <v>394</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -6406,31 +6083,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>386</v>
+        <v>324</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>394</v>
+        <v>327</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -6438,7 +6115,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>398</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>34</v>
@@ -6450,19 +6127,19 @@
         <v>376</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>44</v>
+        <v>400</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10">
@@ -6470,31 +6147,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="F10" s="3">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>291</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
@@ -6502,31 +6179,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>403</v>
+        <v>158</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>376</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>82</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12">
@@ -6534,31 +6211,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>34</v>
+        <v>413</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>291</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -6566,31 +6243,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>158</v>
+        <v>419</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="F13" s="3">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -6598,31 +6275,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>158</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>417</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15">
@@ -6630,31 +6307,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -6662,31 +6339,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>180</v>
+        <v>432</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>198</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -6694,31 +6371,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>427</v>
+        <v>248</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18">
@@ -6726,31 +6403,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F18" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -6758,31 +6435,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>268</v>
+        <v>175</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>376</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20">
@@ -6790,31 +6467,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>286</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21">
@@ -6822,31 +6499,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>445</v>
+        <v>111</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>82</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W35.xlsx
+++ b/reports/devops-jobs-israel-2026-W35.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="476">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28T18:33:05</t>
+    <t xml:space="preserve">2026-08-30T11:48:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -234,6 +234,18 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8161565&amp;gh_jid=8161565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior AI Infrastructure Engineer</t>
   </si>
   <si>
@@ -411,750 +423,738 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Infra Engineer</t>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Axonius</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, Python, MongoDB, Kafka, Security, Snowflake, Databricks, Airflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537525003</t>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scytale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ControlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer Cloud Engineering Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-engineering-team-at-walkme-4413022554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4459692412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discreet Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4459308737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4459018156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cust2mate-a2z-nasdaq-az-4459724930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SecuriThings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Software Engineer - Chip Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-software-engineer-chip-design-at-nvidia-4441368534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Solo Role (Site Only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-solo-role-site-only-at-autobrains-technologies-4457485304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wenrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SciPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-ai-infrastructure-engineer-at-gong-4422913939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer - AI Platforms (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-ai-platforms-cortex-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4451555123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Client Facing System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarity Sec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4458834488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Operations Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Terraform, Ansible, Docker, CI/CD, Linux, Python, Bash/Shell, Prometheus, Grafana, Security, Observability</t>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7818899003</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7537524003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science &amp; ML-Ops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security, Observability, AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8539030002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-aidoc-4449444867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer- Posture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-posture-at-dream-4456806167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Echo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4449116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-log-on-software-4457221102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - FedRAMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ControlUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-fedramp-at-controlup-4457759634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-comblack-4459877158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4455089559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4455859764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-walkme-4380911237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SecuriThings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-securithings-4446720959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-at-pango-4456919037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discreet Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-discreet-company-4457746809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead (37248)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-37248-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4459803825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fig-security-4456853693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-gong-4457888927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-kaltura-4442712745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-fetcherr-4450173695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zadara-4448858731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-zenity-4455197109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4456599044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-immunai-4459018156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Site Reliability Engineer - Imunify Reliability Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lead-site-reliability-engineer-imunify-reliability-platform-at-jobgether-4456887109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-sre-engineer-at-axon-4440000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-ai-4455899737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-ai-4457226217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE &amp; Linux Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-linux-infrastructure-engineer-at-mobileye-4439143553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE (IT Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-sre-it-infrastructure-at-palo-alto-networks-4387086808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4459308737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kaltura-4445905827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SciPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-sciplay-4391151881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KMS Lighthouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-kms-lighthouse-4456815057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4448296220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (DevOps Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-devops-platform-at-palo-alto-networks-4432205784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-controlup-4457749718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4455068343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scytale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scytale-4449488382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-log-on-software-4457241389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wenrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-wenrix-4459896578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Automation &amp; Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-automation-platform-engineer-at-jobgether-4458378160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client Facing System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarity Sec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/client-facing-system-administrator-at-clarity-sec-4455896777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4455193277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Engineer (25367)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-engineer-25367-at-yael-group-4457233394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Team Leader – Cloud Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-leader-%E2%80%93-cloud-platform-at-genpact-4456917658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, CI/CD, Git, Terraform/IaC, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
   </si>
   <si>
@@ -1197,21 +1197,6 @@
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Bash/Shell, AWS, GCP, Cloud (any), Networking, Monitoring, Virtualization, Active Directory</t>
   </si>
   <si>
@@ -1227,6 +1212,24 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -1290,6 +1293,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -1302,6 +1317,39 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4458547603</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1326,33 +1374,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4457742934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -1362,7 +1383,7 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
     <t xml:space="preserve">Nebius</t>
@@ -1371,19 +1392,7 @@
     <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1392,10 +1401,10 @@
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -1562,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
@@ -1570,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1578,7 +1587,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -1586,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>1061</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="10">
@@ -1658,7 +1667,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1666,7 +1675,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1685,23 +1694,23 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>436</v>
+        <v>375</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1709,12 +1718,12 @@
         <v>380</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1722,7 +1731,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1741,55 +1750,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>457</v>
+        <v>359</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>283</v>
+        <v>461</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -1797,31 +1806,31 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1829,7 +1838,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1837,15 +1846,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>466</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
@@ -1853,15 +1862,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>463</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1889,13 +1898,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2">
@@ -1903,13 +1912,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>18.8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1918,88 +1927,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
-        <v>38.7</v>
+        <v>34.9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.3</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>43.1</v>
+        <v>33.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>16.4</v>
+        <v>18.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2011,7 +2020,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2083,7 +2092,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2115,7 +2124,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -2147,7 +2156,7 @@
         <v>51</v>
       </c>
       <c r="J4" s="3">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -2179,7 +2188,7 @@
         <v>40</v>
       </c>
       <c r="J5" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2211,7 +2220,7 @@
         <v>40</v>
       </c>
       <c r="J6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -2243,7 +2252,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -2275,7 +2284,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2307,7 +2316,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2315,10 +2324,10 @@
         <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>48</v>
@@ -2327,27 +2336,27 @@
         <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="J10" s="3">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>48</v>
@@ -2359,27 +2368,27 @@
         <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="3">
         <v>77</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="3">
-        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
@@ -2403,7 +2412,7 @@
         <v>82</v>
       </c>
       <c r="J12" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -2411,7 +2420,7 @@
         <v>83</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
@@ -2435,7 +2444,7 @@
         <v>86</v>
       </c>
       <c r="J13" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -2443,7 +2452,7 @@
         <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>48</v>
@@ -2464,21 +2473,21 @@
         <v>89</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J14" s="3">
-        <v>75</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>48</v>
@@ -2487,30 +2496,30 @@
         <v>37</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="J15" s="3">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>48</v>
@@ -2528,21 +2537,21 @@
         <v>98</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>48</v>
@@ -2551,19 +2560,19 @@
         <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="J17" s="3">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -2571,10 +2580,10 @@
         <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>48</v>
@@ -2583,30 +2592,30 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J18" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>48</v>
@@ -2615,65 +2624,65 @@
         <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="J19" s="3">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J20" s="3">
-        <v>54</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>42</v>
@@ -2691,7 +2700,7 @@
         <v>119</v>
       </c>
       <c r="J21" s="3">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -2699,95 +2708,95 @@
         <v>120</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J22" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="J23" s="3">
-        <v>77</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J24" s="3">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25">
@@ -2795,10 +2804,10 @@
         <v>134</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>48</v>
@@ -2807,30 +2816,30 @@
         <v>37</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J25" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>48</v>
@@ -2839,30 +2848,30 @@
         <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="J26" s="3">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>48</v>
@@ -2871,94 +2880,92 @@
         <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J28" s="3">
-        <v>82</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>151</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>156</v>
       </c>
       <c r="J29" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>48</v>
@@ -2966,124 +2973,122 @@
       <c r="E30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>122</v>
-      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="J30" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="J32" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J33" s="3">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>42</v>
@@ -3093,21 +3098,21 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>158</v>
@@ -3116,34 +3121,34 @@
         <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="J35" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>42</v>
@@ -3153,116 +3158,116 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="J36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J38" s="3">
         <v>86</v>
-      </c>
-      <c r="J38" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="J39" s="3">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>48</v>
@@ -3275,60 +3280,60 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="J40" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3338,108 +3343,108 @@
         <v>198</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>168</v>
+        <v>52</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J43" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>207</v>
+        <v>130</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>209</v>
+        <v>90</v>
       </c>
       <c r="J45" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>158</v>
@@ -3448,28 +3453,28 @@
         <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>158</v>
@@ -3480,20 +3485,18 @@
       <c r="E47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="J47" s="3">
-        <v>89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3504,7 +3507,7 @@
         <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
@@ -3517,27 +3520,27 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="J48" s="3">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="D49" s="3" t="s">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>42</v>
@@ -3547,54 +3550,54 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>227</v>
+        <v>48</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>229</v>
+        <v>163</v>
       </c>
       <c r="J50" s="3">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -3607,43 +3610,43 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>86</v>
+        <v>227</v>
       </c>
       <c r="J51" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53">
@@ -3651,10 +3654,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>48</v>
@@ -3667,57 +3670,57 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3727,40 +3730,40 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="J55" s="3">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
       <c r="J56" s="3">
         <v>4</v>
@@ -3768,46 +3771,46 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="J57" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>207</v>
+        <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3817,21 +3820,21 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>209</v>
+        <v>90</v>
       </c>
       <c r="J58" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>158</v>
@@ -3847,57 +3850,57 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="J59" s="3">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>109</v>
+        <v>201</v>
       </c>
       <c r="J60" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>206</v>
+        <v>261</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>207</v>
+        <v>36</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>37</v>
@@ -3907,27 +3910,27 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>61</v>
       </c>
       <c r="J61" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
@@ -3937,27 +3940,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>256</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>158</v>
+        <v>264</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
@@ -3967,27 +3970,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="J63" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -3997,100 +4000,102 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>158</v>
+        <v>273</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>48</v>
+        <v>274</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="J65" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>273</v>
+        <v>158</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="J67" s="3">
         <v>2</v>
@@ -4098,16 +4103,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>275</v>
+        <v>52</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>276</v>
+        <v>158</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
@@ -4117,27 +4122,27 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
@@ -4147,83 +4152,81 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>279</v>
+        <v>52</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>281</v>
+        <v>158</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>282</v>
+        <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>283</v>
-      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J70" s="3">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>86</v>
+        <v>293</v>
       </c>
       <c r="J71" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>288</v>
+        <v>52</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>158</v>
@@ -4232,94 +4235,96 @@
         <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>86</v>
+        <v>296</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>292</v>
+        <v>74</v>
       </c>
       <c r="J73" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>164</v>
+        <v>296</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>297</v>
+        <v>158</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>42</v>
@@ -4329,57 +4334,57 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>61</v>
+        <v>306</v>
       </c>
       <c r="J75" s="3">
-        <v>2</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>168</v>
+        <v>307</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>299</v>
+        <v>188</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>42</v>
@@ -4389,117 +4394,119 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>267</v>
+        <v>74</v>
       </c>
       <c r="J78" s="3">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>306</v>
+        <v>188</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="J79" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="J80" s="3">
-        <v>81</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>311</v>
+        <v>52</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>178</v>
+        <v>320</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>37</v>
@@ -4509,57 +4516,57 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>86</v>
+        <v>324</v>
       </c>
       <c r="J82" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>42</v>
@@ -4569,87 +4576,89 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>316</v>
+        <v>90</v>
       </c>
       <c r="J83" s="3">
-        <v>84</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>319</v>
+        <v>166</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>173</v>
+        <v>333</v>
       </c>
       <c r="J85" s="3">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>210</v>
+        <v>334</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>174</v>
+        <v>335</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>42</v>
@@ -4659,291 +4668,139 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>326</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="J88" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>261</v>
+        <v>344</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="J89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>182</v>
-      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J90" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J91" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J92" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J93" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J94" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J95" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J95"/>
+  <autoFilter ref="A1:J90"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5034,11 +4891,6 @@
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
-    <hyperlink ref="H91" r:id="rId90"/>
-    <hyperlink ref="H92" r:id="rId91"/>
-    <hyperlink ref="H93" r:id="rId92"/>
-    <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5046,8 +4898,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="51" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5080,13 +4932,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5094,15 +4946,15 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>158</v>
@@ -5113,18 +4965,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>299</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5132,18 +4984,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>300</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>178</v>
+        <v>218</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5151,15 +5003,15 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>312</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>329</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>158</v>
@@ -5170,17 +5022,97 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>330</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5194,71 +5126,71 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>352</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>354</v>
+        <v>189</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>283</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5266,15 +5198,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>358</v>
+        <v>275</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5282,7 +5214,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>126</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5290,15 +5222,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5306,15 +5238,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -5336,12 +5268,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5349,7 +5281,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3">
         <v>4</v>
@@ -5357,15 +5289,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5373,7 +5305,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5381,15 +5313,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
         <v>2</v>
@@ -5397,7 +5329,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -5405,7 +5337,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5413,7 +5345,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5421,7 +5353,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5429,7 +5361,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5437,7 +5369,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5445,7 +5377,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5453,7 +5385,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5467,23 +5399,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -5491,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3">
         <v>18.6</v>
@@ -5505,13 +5437,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3">
-        <v>16.8</v>
+        <v>10.9</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -5519,10 +5451,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5533,13 +5465,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="C5" s="3">
-        <v>10.4</v>
+        <v>7.4</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5547,10 +5479,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -5575,7 +5507,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3">
         <v>5.8</v>
@@ -5589,7 +5521,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C9" s="3">
         <v>5.3</v>
@@ -5603,7 +5535,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C10" s="3">
         <v>5.3</v>
@@ -5617,7 +5549,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C11" s="3">
         <v>5.0</v>
@@ -5631,13 +5563,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>325</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5645,13 +5577,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="C13" s="3">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D13" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5659,10 +5591,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -5673,13 +5605,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5687,7 +5619,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5713,21 +5645,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3">
@@ -5735,10 +5667,10 @@
         <v>42</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -5746,10 +5678,10 @@
         <v>37</v>
       </c>
       <c r="B4" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5768,7 +5700,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
@@ -5776,12 +5708,12 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3">
         <v>17</v>
@@ -5789,7 +5721,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5797,15 +5729,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>222</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5813,23 +5745,23 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>227</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -5856,10 +5788,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5871,10 +5803,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5891,31 +5823,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>134</v>
+        <v>374</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>136</v>
+        <v>377</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3">
@@ -5929,7 +5861,7 @@
         <v>379</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>380</v>
@@ -5947,7 +5879,7 @@
         <v>382</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -5964,7 +5896,7 @@
         <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -5979,7 +5911,7 @@
         <v>386</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5">
@@ -5996,7 +5928,7 @@
         <v>158</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -6011,7 +5943,7 @@
         <v>390</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -6051,31 +5983,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="3">
+        <v>68</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>396</v>
+        <v>330</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -6083,31 +6015,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>325</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>86</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -6115,31 +6047,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>35</v>
+        <v>399</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F9" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10">
@@ -6147,10 +6079,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>158</v>
@@ -6162,16 +6094,16 @@
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11">
@@ -6179,31 +6111,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>158</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F11" s="3">
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12">
@@ -6211,28 +6143,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F12" s="3">
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>61</v>
@@ -6243,31 +6175,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F13" s="3">
         <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
@@ -6275,31 +6207,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15">
@@ -6307,31 +6239,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>158</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F15" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>82</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16">
@@ -6339,31 +6271,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>40</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17">
@@ -6371,31 +6303,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>248</v>
+        <v>440</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>158</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18">
@@ -6403,28 +6335,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>441</v>
+        <v>158</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>436</v>
+        <v>375</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>86</v>
@@ -6435,31 +6367,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>175</v>
+        <v>448</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>156</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6467,31 +6399,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>436</v>
+        <v>375</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21">
@@ -6499,31 +6431,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>268</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F21" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>454</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
